--- a/退職所得計算_excel.xlsx
+++ b/退職所得計算_excel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\30_個人年金\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\40_個人年金\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B5C689-CF5B-4F5F-9675-0ADEF5123068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FB5D46-40D1-4BE5-8DB3-54D951EDA27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{E74CE8F4-0FCE-41F4-83DC-0C96164E4C1D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>入社年月日</t>
     <phoneticPr fontId="1"/>
@@ -325,6 +325,9 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>税額＝（課税退職所得金額×税率－控除額）×102.1％</t>
+  </si>
 </sst>
 </file>
 
@@ -334,7 +337,7 @@
     <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="177" formatCode="#&quot;年&quot;"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -513,7 +516,7 @@
     <xf numFmtId="176" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -564,7 +567,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$O$10:$Q$19" spid="_x0000_s1050"/>
+                  <a14:cameraTool cellRange="$O$10:$Q$19" spid="_x0000_s1068"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -629,7 +632,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$S$10:$T$17" spid="_x0000_s1051"/>
+                  <a14:cameraTool cellRange="$S$10:$T$17" spid="_x0000_s1069"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -694,7 +697,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$V$10:$V$14" spid="_x0000_s1052"/>
+                  <a14:cameraTool cellRange="$V$10:$V$14" spid="_x0000_s1070"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1096,14 +1099,14 @@
         <v>1</v>
       </c>
       <c r="B4" s="14">
-        <v>49490</v>
+        <v>49460</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="str">
         <f>DATEDIF(B2, B4, "Y") &amp; "歳" &amp; DATEDIF(B2, B4, "YM") &amp; "ヶ月"</f>
-        <v>65歳1ヶ月</v>
+        <v>65歳0ヶ月</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.4">
@@ -1196,8 +1199,11 @@
         <v>25</v>
       </c>
       <c r="B11" s="10">
-        <f>FLOOR((B8-B10)*B9*1.021, 1)</f>
+        <f>FLOOR((B8*B9-B10)*1.021, 1)</f>
         <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>15</v>
@@ -1476,8 +1482,13 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7VaXyT2pGjmiARaXmDu8IfavZ5fFQR1+isGVtsfnAfTSyEjKuviZ3q/J6jMK/n8/41ZxqNrScCBTQI0dOaKDvA==" saltValue="jGzOcG2LTZ8WQD4CKP+NGw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B4" xr:uid="{663D6727-6FD9-4F6F-BDEE-DEC0DF39DFE9}">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="A34" r:id="rId1" xr:uid="{0D5994F3-91EE-47BF-B36F-A23B0B7DAB43}"/>
     <hyperlink ref="A32" r:id="rId2" xr:uid="{E85E5A50-F9A6-483A-897B-03DE48B6083C}"/>
